--- a/wooclap/imports/05_Constraints_Part_1.xlsx
+++ b/wooclap/imports/05_Constraints_Part_1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$5</definedName>

--- a/wooclap/imports/05_Constraints_Part_1.xlsx
+++ b/wooclap/imports/05_Constraints_Part_1.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L02-C01 · Two exams must use different rooms. Each can use room 1 or room 2. Which room assignment is allowed?</t>
+          <t>L02-C01 · A, B and C each have domain {1,2,3}. The rules are A &lt; B and B ≠ C. Only A = 2 is assigned. Which statement about this partial assignment is correct?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Both exams in room 1.</t>
+          <t>It already violates A &lt; B, because B has no assigned value.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Both exams in room 2.</t>
+          <t>It is a solution, because no rule has been violated yet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Exam A in room 1; exam B in room 2.</t>
+          <t>Neither rule is evaluable yet; one possible completion is B = 3, C = 1.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Exam A in room 3; exam B in room 1.</t>
+          <t>Both rules are satisfied, because each has at least one possible supporting pair.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L02-C02 · While making a timetable, you put two classes in the same room at the same time. What is a sensible next step?</t>
+          <t>L02-C02 · X₁, X₂ and X₃ each have domain {0,1,2}. The rules are X₁ &lt; 2, X₂ &gt; 0 and X₃ &lt; X₁. DFS assigns X₁ first and tries X₁ = 2. What can it prune immediately, without propagation?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Undo one of those choices and try another.</t>
+          <t>All 9 completions of this branch: X₁ &lt; 2 is already false.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Keep the clash and assume a later choice will remove it.</t>
+          <t>Only the 3 completions with X₂ = 0: X₃ is still unassigned.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Conclude that no timetable could ever work.</t>
+          <t>All 27 assignments: a false unary rule makes the whole CSP impossible.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Stop checking room conflicts for the remaining classes.</t>
+          <t>Nothing yet: every rule must wait until all three variables are assigned.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L02-C03 · A task must finish before 3 pm. Its possible finish times are 1 pm, 2 pm and 3 pm. Which time can you rule out?</t>
+          <t>L02-C03 · A, B and C each start with domain {1,2,3,4}; the rules are A &lt; B and B &lt; C. Repeatedly remove values with no support in a rule, until no domain changes. What remains?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1 pm.</t>
+          <t>A = {1,2,3}, B = {2,3}, C = {2,3,4}.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3 pm.</t>
+          <t>A = {1,2}, B = {2,3}, C = {3,4}.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2 pm.</t>
+          <t>A = {1}, B = {2}, C = {3}: propagation chooses the smallest solution.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>None of them.</t>
+          <t>A = {1,2,3}, B = {1,2,3,4}, C = {2,3,4}.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L02-C04 · Three exams must all use different rooms, but only two rooms are available. Can you assign a room to every exam?</t>
+          <t>L02-C04 · A, B and C each have domain {1,2}. The three separate binary rules are A = B, B = C and A ≠ C. What happens if we enforce arc consistency on each rule?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Yes, by putting all three exams in room 1.</t>
+          <t>All domains become empty: arc consistency combines the two equalities into A = C.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Yes, because each pair of exams could fit in two rooms when considered alone.</t>
+          <t>A = 1 is removed, but A = 2 remains as a solution.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>No. Three different rooms would be needed.</t>
+          <t>All values remain supported in each rule, although no total assignment satisfies all three.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Yes, as long as the rooms have different names.</t>
+          <t>All values remain, which proves that a solution exists.</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
